--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TKFaUJ9TTJEYTJ9Y</t>
+          <t>SJEaUJ9SSJCYSJ9Y</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>55gBA4d974dAA4d7</t>
+          <t>34dAA4d964dAA4d7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZojVfngTZngTdngT</t>
+          <t>ZngUengTZngTbngT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:32</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:32</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SJEaUJ9SSJCYSJ9Y</t>
+          <t>RLBZSI9YRIAYRI9Y</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>34dAA4d964dAA4d7</t>
+          <t>96eAA3b833bA93b7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZngUengTZngTbngT</t>
+          <t>YphTbmeTZmeTameT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RLBZSI9YRIAYRI9Y</t>
+          <t>RKBaSJ9TRJAYRJ9Y</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>96eAA3b833bA93b7</t>
+          <t>95eBA4b934bA94b7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YphTbmeTZmeTameT</t>
+          <t>YohVbneTZneTaneT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RKBaSJ9TRJAYRJ9Y</t>
+          <t>UJIaWJ9SUJGYUJ9Y</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>95eBA4b934bA94b7</t>
+          <t>74fAB4f994fAA4f7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YohVbneTZneTaneT</t>
+          <t>ZniUiniTZniTfniT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -782,7 +782,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v3.04</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -818,7 +818,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -836,7 +836,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>CameraPowerCycle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2025/12/03/2025-12-03__15-00-08_VisImg_Dark_d1024x1024x0010_b1_e000200000us.sp</t>
+          <t>/sssp/data/2026/03/16/2026-03-16__19-43-53_VisImg_CameraPowerCycle_d2048x2048x0001_b1_e000200000us.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -926,7 +926,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -944,7 +944,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -980,7 +980,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -998,7 +998,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1016,7 +1016,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1070,7 +1070,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>818089246</t>
+          <t>827005470</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1088,7 +1088,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>182000000</t>
+          <t>769000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UJIaWJ9SUJGYUJ9Y</t>
+          <t>kAAIn08Fk7AFk77F</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
+          <t>HDU checksum updated 2026-04-15T12:51:11</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-04-15T12:51:11</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>74fAB4f994fAA4f7</t>
+          <t>LkLHLiLFLiLFLiLF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
+          <t>HDU checksum updated 2026-04-15T12:51:11</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2751485292</t>
+          <t>3495429948</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-04-15T12:51:11</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZniUiniTZniTfniT</t>
+          <t>5O826L825L825L82</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
+          <t>HDU checksum updated 2026-04-15T12:51:11</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2339345775</t>
+          <t>674767643</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-04-15T12:51:11</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -782,7 +782,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.04</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -836,7 +836,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CameraPowerCycle</t>
+          <t>G1299384497902599936</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/03/16/2026-03-16__19-43-53_VisImg_CameraPowerCycle_d2048x2048x0001_b1_e000200000us.sp</t>
+          <t>2026-07-12__02-42-32.525_VisImg_G1299384497902599936_d1280x1280x0010_b1_e000200000us.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -926,7 +926,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -944,7 +944,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -980,7 +980,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -998,7 +998,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1016,7 +1016,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1070,7 +1070,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>827005470</t>
+          <t>837139385</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1088,7 +1088,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>769000000</t>
+          <t>525000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kAAIn08Fk7AFk77F</t>
+          <t>1EKQ19KO1EKO19KO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-04-15T12:51:11</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-04-15T12:51:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LkLHLiLFLiLFLiLF</t>
+          <t>UZ6RaY6RWY6RaY6R</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-04-15T12:51:11</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3495429948</t>
+          <t>4290961373</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-04-15T12:51:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5O826L825L825L82</t>
+          <t>mL80mJ70mJ70mJ70</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-04-15T12:51:11</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>674767643</t>
+          <t>490153783</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-04-15T12:51:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1EKQ19KO1EKO19KO</t>
+          <t>1CNP49KN1CKN19KN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UZ6RaY6RWY6RaY6R</t>
+          <t>WY9QaX6QXX6QaX6Q</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mL80mJ70mJ70mJ70</t>
+          <t>mKAopI0omI7omI7o</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level0-ffi_visda.xlsx
@@ -1160,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1CNP49KN1CKN19KN</t>
+          <t>0DMQ39JN0CJN09JN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WY9QaX6QXX6QaX6Q</t>
+          <t>UZ8RaX5QVX5QaX5Q</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mKAopI0omI7omI7o</t>
+          <t>lL9poI6olI6olI6o</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
